--- a/paper_aaai27/figures/overall_baseline_comparison/overall_baseline_comparison.xlsx
+++ b/paper_aaai27/figures/overall_baseline_comparison/overall_baseline_comparison.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$AM$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Seed_Detail'!$A$1:$P$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$AM$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Seed_Detail'!$A$1:$P$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coverage'!$A$1:$P$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,16 +25,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -60,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -68,23 +65,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM34"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -744,74 +735,74 @@
         <v>0.0001329884371652263</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr"/>
@@ -869,74 +860,74 @@
         <v>0.01129542932907935</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr"/>
@@ -994,74 +985,74 @@
         <v>0.007276093366947464</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr"/>
       <c r="AF4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr"/>
@@ -1122,35 +1113,35 @@
         <v>6</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
@@ -1158,11 +1149,11 @@
         <v>6</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr"/>
@@ -1170,11 +1161,11 @@
         <v>6</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr"/>
@@ -1182,11 +1173,11 @@
         <v>6</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr"/>
@@ -1247,11 +1238,11 @@
         <v>10</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr"/>
@@ -1259,11 +1250,11 @@
         <v>10</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr"/>
@@ -1271,11 +1262,11 @@
         <v>10</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
@@ -1283,11 +1274,11 @@
         <v>10</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
@@ -1295,11 +1286,11 @@
         <v>10</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr"/>
@@ -1307,11 +1298,11 @@
         <v>10</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM6" s="2" t="inlineStr"/>
@@ -1333,110 +1324,110 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.138296013526316</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.01276200638817466</v>
+        <v>0.01415666024319724</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.1767345552142124</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.01516242486190873</v>
+        <v>0.01652362430204563</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.2255074969884014</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.01559648063463602</v>
+        <v>0.01593465142101319</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.104269944247113</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.009130121854534547</v>
+        <v>0.01130047301124758</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1166146148397607</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.009966854450299475</v>
+        <v>0.01195959205509683</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1288879979531413</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.01008691885414054</v>
+        <v>0.01185748680857823</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
       <c r="AB7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr"/>
       <c r="AF7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL7" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM7" s="2" t="inlineStr"/>
@@ -1497,11 +1488,11 @@
         <v>8</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr"/>
@@ -1509,11 +1500,11 @@
         <v>9</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
@@ -1521,11 +1512,11 @@
         <v>9</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
@@ -1533,11 +1524,11 @@
         <v>7</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -1545,11 +1536,11 @@
         <v>7</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr"/>
@@ -1557,11 +1548,11 @@
         <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM8" s="2" t="inlineStr"/>
@@ -1619,74 +1610,74 @@
         <v>0.00928345741065474</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL9" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM9" s="2" t="inlineStr"/>
@@ -1699,7 +1690,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1708,110 +1699,110 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.1135992899136741</v>
+        <v>0.02407772474090461</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.01007486997222141</v>
+        <v>0.008561942967011923</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1550661556410874</v>
+        <v>0.05197384604480621</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.01175700941387082</v>
+        <v>0.01165519454888393</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.2120591378272964</v>
+        <v>0.09969378147700399</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.02163311824729574</v>
+        <v>0.01372328444948982</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.08210494374101648</v>
+        <v>0.01445781448292138</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.006938549193905657</v>
+        <v>0.005678727441069768</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.09549211646806803</v>
+        <v>0.02336007356033647</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.007404175980332763</v>
+        <v>0.00611668072203269</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.109834488844435</v>
+        <v>0.0352587695310481</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.009936467612535112</v>
+        <v>0.006635279243747636</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM10" s="2" t="inlineStr"/>
@@ -1824,119 +1815,119 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>USIM</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025,2026,2027</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.1135992899136741</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.01007486997222141</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.1550661556410874</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.01175700941387082</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.2120591378272964</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.02163311824729574</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.08210494374101648</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.006938549193905657</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.09549211646806803</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0.007404175980332763</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0.109834488844435</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0.009936467612535112</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>0.187962169287402</v>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>SEMCo</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2025,2026,2027</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0.187962169287402</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.01154150231346956</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.2501841934446253</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.0140450505742366</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.3328092146950845</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0.01668522782745853</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0.1346698803739343</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.007361859641104038</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>0.1547627312639487</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0.008210248396456218</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>0.1755312177412371</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>0.008837458043275194</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>0.4535701447134395</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>ALDI</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr"/>
       <c r="AF11" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL11" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="AM11" s="2" t="inlineStr"/>
@@ -1949,7 +1940,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1958,135 +1949,123 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.1042984890880549</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.01469607767742897</v>
+        <v>0.01154150231346956</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1567872678150372</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.01522898291689484</v>
+        <v>0.0140450505742366</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.2315276675992748</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.01782895658256258</v>
+        <v>0.01668522782745853</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.07107613756271405</v>
+        <v>0.1346698803739343</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.01001281707862742</v>
+        <v>0.007361859641104038</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.08794009913710506</v>
+        <v>0.1547627312639487</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.01011555091760084</v>
+        <v>0.008210248396456218</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.1067399749750467</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.01080271860937664</v>
+        <v>0.008837458043275194</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.4535701447134395</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>-0.7700499243530469</v>
-      </c>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.4967644493769034</v>
+        <v>0.2501841934446253</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>-0.6843830752951483</v>
-      </c>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>0.5384655355604333</v>
+        <v>0.3328092146950845</v>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="n">
-        <v>-0.5700232376835381</v>
-      </c>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
       <c r="AB12" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>0.3807252379786977</v>
+        <v>0.1410979353983361</v>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="n">
-        <v>-0.8133138272102388</v>
-      </c>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
       <c r="AF12" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>0.3947454563554984</v>
+        <v>0.1586131675625427</v>
       </c>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
-        </is>
-      </c>
-      <c r="AI12" s="3" t="n">
-        <v>-0.7772232771239087</v>
-      </c>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>0.4053036444482686</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
-        </is>
-      </c>
-      <c r="AM12" s="3" t="n">
-        <v>-0.7366419561305706</v>
-      </c>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Junyi</t>
+          <t>MOOCCube</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2095,113 +2074,125 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.01641710470647014</v>
+        <v>0.1042984890880549</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0002041218597371534</v>
+        <v>0.01469607767742897</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.0286463965355689</v>
+        <v>0.1567872678150372</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.0009352619649727065</v>
+        <v>0.01522898291689484</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.05189634416519956</v>
+        <v>0.2315276675992748</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.0005907333117423992</v>
+        <v>0.01782895658256258</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.01009944896116269</v>
+        <v>0.07107613756271405</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.0002858210537305364</v>
+        <v>0.01001281707862742</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.01400393151511998</v>
+        <v>0.08794009913710506</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.0004978907952707118</v>
+        <v>0.01011555091760084</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.0198568240005371</v>
+        <v>0.1067399749750467</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.0003892155668978831</v>
+        <v>0.01080271860937664</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0.1482118552052219</v>
+        <v>0.187962169287402</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>-0.4451091435927293</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0.2501841934446253</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>-0.3733126555425662</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>0.3328092146950845</v>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>-0.3043231455853845</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="3" t="n">
+        <v>0.1410979353983361</v>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
           <t>CGRC</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>0.217028724493082</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="AE13" s="3" t="n">
+        <v>-0.4962638017200058</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="3" t="n">
+        <v>0.1586131675625427</v>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
         <is>
           <t>CGRC</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v>0.3234686837097654</v>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>LightGCN</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC13" s="3" t="n">
-        <v>0.09983050872515496</v>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>CGRC</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG13" s="3" t="n">
-        <v>0.1219261595347395</v>
-      </c>
-      <c r="AH13" s="2" t="inlineStr">
-        <is>
-          <t>CGRC</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AI13" s="3" t="n">
+        <v>-0.4455687350015917</v>
+      </c>
       <c r="AJ13" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>0.1447889699961517</v>
+        <v>0.1755312177412371</v>
       </c>
       <c r="AL13" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
-        </is>
-      </c>
-      <c r="AM13" s="2" t="inlineStr"/>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="n">
+        <v>-0.3919031819604895</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2211,7 +2202,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2220,43 +2211,43 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.1291696276229269</v>
+        <v>0.01641710470647014</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.006009647104180509</v>
+        <v>0.0002041218597371534</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1830742296099299</v>
+        <v>0.0286463965355689</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.007165329732507517</v>
+        <v>0.0009352619649727065</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.2615258131840985</v>
+        <v>0.05189634416519956</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.008690224690326372</v>
+        <v>0.0005907333117423992</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.08940518676287273</v>
+        <v>0.01009944896116269</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.003990099730452811</v>
+        <v>0.0002858210537305364</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.1067486675522891</v>
+        <v>0.01400393151511998</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.004328109750825928</v>
+        <v>0.0004978907952707118</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.1264761661098986</v>
+        <v>0.0198568240005371</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.004703747758972871</v>
+        <v>0.0003892155668978831</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -2268,7 +2259,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0.217028724493082</v>
@@ -2280,7 +2271,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -2292,7 +2283,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AC14" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -2304,7 +2295,7 @@
       </c>
       <c r="AE14" s="2" t="inlineStr"/>
       <c r="AF14" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AG14" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -2316,7 +2307,7 @@
       </c>
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -2336,7 +2327,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2345,43 +2336,43 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.07445473952411581</v>
+        <v>0.1291696276229269</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.001928053294480697</v>
+        <v>0.006009647104180509</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1272276157572894</v>
+        <v>0.1830742296099299</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.004439248983455238</v>
+        <v>0.007165329732507517</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.2096250783642493</v>
+        <v>0.2615258131840985</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.00806110002870401</v>
+        <v>0.008690224690326372</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.04638254090073526</v>
+        <v>0.08940518676287273</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.0007926148153590942</v>
+        <v>0.003990099730452811</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.0632965940715897</v>
+        <v>0.1067486675522891</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.001497791549909053</v>
+        <v>0.004328109750825928</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.08397456880700804</v>
+        <v>0.1264761661098986</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.00226465388240737</v>
+        <v>0.004703747758972871</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -2393,7 +2384,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>0.217028724493082</v>
@@ -2405,7 +2396,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -2417,7 +2408,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AC15" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -2429,7 +2420,7 @@
       </c>
       <c r="AE15" s="2" t="inlineStr"/>
       <c r="AF15" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG15" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -2441,7 +2432,7 @@
       </c>
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -2461,7 +2452,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2470,43 +2461,43 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.1338480470790703</v>
+        <v>0.07445473952411581</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.01577919662779195</v>
+        <v>0.001928053294480697</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2113041714528844</v>
+        <v>0.1272276157572894</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.02084096026032069</v>
+        <v>0.004439248983455238</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.3234686837097654</v>
+        <v>0.2096250783642493</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.02811994748071283</v>
+        <v>0.00806110002870401</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.08794231223126825</v>
+        <v>0.04638254090073526</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.01114186749967109</v>
+        <v>0.0007926148153590942</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.1127839265363623</v>
+        <v>0.0632965940715897</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.01276219435819356</v>
+        <v>0.001497791549909053</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.1409888329484801</v>
+        <v>0.08397456880700804</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.01460350306171339</v>
+        <v>0.00226465388240737</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -2518,7 +2509,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>0.217028724493082</v>
@@ -2530,7 +2521,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -2542,7 +2533,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AC16" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -2554,7 +2545,7 @@
       </c>
       <c r="AE16" s="2" t="inlineStr"/>
       <c r="AF16" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG16" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -2566,7 +2557,7 @@
       </c>
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -2586,7 +2577,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2595,43 +2586,43 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.01647074808136643</v>
+        <v>0.1338480470790703</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.001665789036805798</v>
+        <v>0.01577919662779195</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.02806694052576318</v>
+        <v>0.2113041714528844</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.002402120300574845</v>
+        <v>0.02084096026032069</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.06152063251432405</v>
+        <v>0.3234686837097654</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.00140783553169201</v>
+        <v>0.02811994748071283</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01061719409655738</v>
+        <v>0.08794231223126825</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.001079998476898039</v>
+        <v>0.01114186749967109</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.01431519252312917</v>
+        <v>0.1127839265363623</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.001319372911872983</v>
+        <v>0.01276219435819356</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.02257694588788622</v>
+        <v>0.1409888329484801</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.0005122731511968702</v>
+        <v>0.01460350306171339</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -2643,7 +2634,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>0.217028724493082</v>
@@ -2655,7 +2646,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -2667,7 +2658,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
       <c r="AB17" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC17" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -2679,7 +2670,7 @@
       </c>
       <c r="AE17" s="2" t="inlineStr"/>
       <c r="AF17" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG17" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -2691,7 +2682,7 @@
       </c>
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -2711,7 +2702,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2720,43 +2711,43 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.1157416693793514</v>
+        <v>0.01647074808136643</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.004876468597201551</v>
+        <v>0.001665789036805798</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.1854719491613628</v>
+        <v>0.02806694052576318</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.007740414381588714</v>
+        <v>0.002402120300574845</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.2935009128045321</v>
+        <v>0.06152063251432405</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.009157969300862049</v>
+        <v>0.00140783553169201</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.07485267636739255</v>
+        <v>0.01061719409655738</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.003134638829383159</v>
+        <v>0.001079998476898039</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.09719393558350309</v>
+        <v>0.01431519252312917</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.004072046154718698</v>
+        <v>0.001319372911872983</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1243354824844195</v>
+        <v>0.02257694588788622</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.004423112914553934</v>
+        <v>0.0005122731511968702</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -2768,7 +2759,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0.217028724493082</v>
@@ -2780,7 +2771,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -2792,7 +2783,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AC18" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -2804,7 +2795,7 @@
       </c>
       <c r="AE18" s="2" t="inlineStr"/>
       <c r="AF18" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG18" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -2816,7 +2807,7 @@
       </c>
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -2836,7 +2827,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2845,43 +2836,43 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.03156922415297889</v>
+        <v>0.1157416693793514</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.006276739206525104</v>
+        <v>0.004876468597201551</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.05583558723619485</v>
+        <v>0.1854719491613628</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.009588959647473177</v>
+        <v>0.007740414381588714</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.09569226427459004</v>
+        <v>0.2935009128045321</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.0122057091129053</v>
+        <v>0.009157969300862049</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01922932832597288</v>
+        <v>0.07485267636739255</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.004415216645286517</v>
+        <v>0.003134638829383159</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.02701879915331286</v>
+        <v>0.09719393558350309</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.005480233638752386</v>
+        <v>0.004072046154718698</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.03702779361798157</v>
+        <v>0.1243354824844195</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>0.006160410385811112</v>
+        <v>0.004423112914553934</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -2893,7 +2884,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0.217028724493082</v>
@@ -2905,7 +2896,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -2917,7 +2908,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
       <c r="AB19" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -2929,7 +2920,7 @@
       </c>
       <c r="AE19" s="2" t="inlineStr"/>
       <c r="AF19" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG19" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -2941,7 +2932,7 @@
       </c>
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -2961,7 +2952,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2970,43 +2961,43 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.1482118552052219</v>
+        <v>0.03156922415297889</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.004286563081647743</v>
+        <v>0.006276739206525104</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.217028724493082</v>
+        <v>0.05583558723619485</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.006921620722203906</v>
+        <v>0.009588959647473177</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.3078500310776894</v>
+        <v>0.09569226427459004</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.009706910318582552</v>
+        <v>0.0122057091129053</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.09983050872515496</v>
+        <v>0.01922932832597288</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.002371089830671321</v>
+        <v>0.004415216645286517</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.1219261595347395</v>
+        <v>0.02701879915331286</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.003315527782941534</v>
+        <v>0.005480233638752386</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.1447889699961517</v>
+        <v>0.03702779361798157</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.004017674490235438</v>
+        <v>0.006160410385811112</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -3018,7 +3009,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>0.217028724493082</v>
@@ -3030,7 +3021,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -3042,7 +3033,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
       <c r="AB20" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -3054,7 +3045,7 @@
       </c>
       <c r="AE20" s="2" t="inlineStr"/>
       <c r="AF20" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AG20" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -3066,7 +3057,7 @@
       </c>
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -3086,7 +3077,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3095,43 +3086,43 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.1221102148244231</v>
+        <v>0.1482118552052219</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.004780432057002061</v>
+        <v>0.004286563081647743</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.1942594843460876</v>
+        <v>0.217028724493082</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.007063406816471677</v>
+        <v>0.006921620722203906</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.2958042295873351</v>
+        <v>0.3078500310776894</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.01279929039180045</v>
+        <v>0.009706910318582552</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.07959259387847385</v>
+        <v>0.09983050872515496</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.003196022473293697</v>
+        <v>0.002371089830671321</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1027600600499671</v>
+        <v>0.1219261595347395</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.003683013413226932</v>
+        <v>0.003315527782941534</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.1282824381488468</v>
+        <v>0.1447889699961517</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0.004853141979820162</v>
+        <v>0.004017674490235438</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -3143,7 +3134,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.217028724493082</v>
@@ -3155,7 +3146,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -3167,7 +3158,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
       <c r="AB21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -3179,7 +3170,7 @@
       </c>
       <c r="AE21" s="2" t="inlineStr"/>
       <c r="AF21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -3191,7 +3182,7 @@
       </c>
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -3211,7 +3202,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3220,43 +3211,43 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.1326348488542907</v>
+        <v>0.04534361463952893</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.02242471470980225</v>
+        <v>0.006569946322290813</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.2113675992327202</v>
+        <v>0.08972827730918416</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.03257813518855254</v>
+        <v>0.01193763861943117</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3212108124900795</v>
+        <v>0.1588709125422972</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.04119718524560208</v>
+        <v>0.01357398228956318</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.08436053570568919</v>
+        <v>0.02605698028234901</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.01555669143741631</v>
+        <v>0.003606118218448139</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.109616024735896</v>
+        <v>0.04024327522349275</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.01880072054534194</v>
+        <v>0.005067242808885214</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.1372288461146241</v>
+        <v>0.05754132874148935</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.02093986555719459</v>
+        <v>0.005516832289479018</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -3268,7 +3259,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>0.217028724493082</v>
@@ -3280,7 +3271,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -3292,7 +3283,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
       <c r="AB22" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AC22" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -3304,7 +3295,7 @@
       </c>
       <c r="AE22" s="2" t="inlineStr"/>
       <c r="AF22" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG22" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -3316,7 +3307,7 @@
       </c>
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -3336,7 +3327,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3345,43 +3336,43 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.09298372548594085</v>
+        <v>0.1221102148244231</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.007802430115226568</v>
+        <v>0.004780432057002061</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.167594350706944</v>
+        <v>0.1942594843460876</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.01420288627666489</v>
+        <v>0.007063406816471677</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.2828863980271339</v>
+        <v>0.2958042295873351</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.01404877911259907</v>
+        <v>0.01279929039180045</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.05558128100257945</v>
+        <v>0.07959259387847385</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.004386673171059125</v>
+        <v>0.003196022473293697</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.0794699590575644</v>
+        <v>0.1027600600499671</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.006473323568670786</v>
+        <v>0.003683013413226932</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.1084082198736293</v>
+        <v>0.1282824381488468</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.006515186365991075</v>
+        <v>0.004853141979820162</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>0.1482118552052219</v>
@@ -3391,11 +3382,9 @@
           <t>CGRC</t>
         </is>
       </c>
-      <c r="S23" s="3" t="n">
-        <v>-0.3726296364269195</v>
-      </c>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>0.217028724493082</v>
@@ -3405,11 +3394,9 @@
           <t>CGRC</t>
         </is>
       </c>
-      <c r="W23" s="3" t="n">
-        <v>-0.2277780229396032</v>
-      </c>
+      <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>0.3234686837097654</v>
@@ -3419,11 +3406,9 @@
           <t>LightGCN</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="n">
-        <v>-0.125459705147359</v>
-      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
       <c r="AB23" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC23" s="3" t="n">
         <v>0.09983050872515496</v>
@@ -3433,11 +3418,9 @@
           <t>CGRC</t>
         </is>
       </c>
-      <c r="AE23" s="3" t="n">
-        <v>-0.4432435363461765</v>
-      </c>
+      <c r="AE23" s="2" t="inlineStr"/>
       <c r="AF23" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG23" s="3" t="n">
         <v>0.1219261595347395</v>
@@ -3447,11 +3430,9 @@
           <t>CGRC</t>
         </is>
       </c>
-      <c r="AI23" s="3" t="n">
-        <v>-0.3482123987106997</v>
-      </c>
+      <c r="AI23" s="2" t="inlineStr"/>
       <c r="AJ23" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>0.1447889699961517</v>
@@ -3461,19 +3442,17 @@
           <t>CGRC</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="n">
-        <v>-0.2512674143858425</v>
-      </c>
+      <c r="AM23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3482,110 +3461,110 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.0008128514466972152</v>
+        <v>0.1326348488542907</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1.767586513852369e-05</v>
+        <v>0.02242471470980225</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.001609678061152421</v>
+        <v>0.2113675992327202</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2.355128622464248e-05</v>
+        <v>0.03257813518855254</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.003136301545613715</v>
+        <v>0.3212108124900795</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>3.594755551264878e-05</v>
+        <v>0.04119718524560208</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.0004979677051587629</v>
+        <v>0.08436053570568919</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>4.914338654237269e-06</v>
+        <v>0.01555669143741631</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.0007521917093370372</v>
+        <v>0.109616024735896</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>4.080261697073254e-06</v>
+        <v>0.01880072054534194</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.001133061783059252</v>
+        <v>0.1372288461146241</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>6.570933101265434e-06</v>
+        <v>0.02093986555719459</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.06046125070311605</v>
+        <v>0.1482118552052219</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.09263628916187981</v>
+        <v>0.217028724493082</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.1366537957489053</v>
+        <v>0.3234686837097654</v>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
       <c r="AB24" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>0.03958768789208255</v>
+        <v>0.09983050872515496</v>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AE24" s="2" t="inlineStr"/>
       <c r="AF24" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>0.04991239337760087</v>
+        <v>0.1219261595347395</v>
       </c>
       <c r="AH24" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>0.0609790833218157</v>
+        <v>0.1447889699961517</v>
       </c>
       <c r="AL24" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="AM24" s="2" t="inlineStr"/>
@@ -3593,12 +3572,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3607,113 +3586,125 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.03580231620689336</v>
+        <v>0.09298372548594085</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.002063726442032366</v>
+        <v>0.007802430115226568</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.05074302287163481</v>
+        <v>0.167594350706944</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.001669890073234396</v>
+        <v>0.01420288627666489</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.0718295784495116</v>
+        <v>0.2828863980271339</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.001998590746909841</v>
+        <v>0.01404877911259907</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.02429929226223913</v>
+        <v>0.05558128100257945</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.001067358815104581</v>
+        <v>0.004386673171059125</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.02912279309908032</v>
+        <v>0.0794699590575644</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0.0009262872527034191</v>
+        <v>0.006473323568670786</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.03441961792674816</v>
+        <v>0.1084082198736293</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0.0009995414302262373</v>
+        <v>0.006515186365991075</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0.06046125070311605</v>
+        <v>0.1482118552052219</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr"/>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>-0.3726296364269195</v>
+      </c>
       <c r="T25" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.09263628916187981</v>
+        <v>0.217028724493082</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr"/>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>-0.2277780229396032</v>
+      </c>
       <c r="X25" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0.1366537957489053</v>
+        <v>0.3234686837097654</v>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr"/>
+          <t>LightGCN</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>-0.125459705147359</v>
+      </c>
       <c r="AB25" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>0.03958768789208255</v>
+        <v>0.09983050872515496</v>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="inlineStr"/>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="AE25" s="3" t="n">
+        <v>-0.4432435363461765</v>
+      </c>
       <c r="AF25" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>0.04991239337760087</v>
+        <v>0.1219261595347395</v>
       </c>
       <c r="AH25" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
-        </is>
-      </c>
-      <c r="AI25" s="2" t="inlineStr"/>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>-0.3482123987106997</v>
+      </c>
       <c r="AJ25" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>0.0609790833218157</v>
+        <v>0.1447889699961517</v>
       </c>
       <c r="AL25" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
-        </is>
-      </c>
-      <c r="AM25" s="2" t="inlineStr"/>
+          <t>CGRC</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="n">
+        <v>-0.2512674143858425</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3723,7 +3714,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3732,43 +3723,43 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.06046125070311605</v>
+        <v>0.0008128514466972152</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.002270552850181354</v>
+        <v>1.767586513852369e-05</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.09263628916187981</v>
+        <v>0.001609678061152421</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.001817303782928136</v>
+        <v>2.355128622464248e-05</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.1366537957489053</v>
+        <v>0.003136301545613715</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.002338016448942837</v>
+        <v>3.594755551264878e-05</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.03958768789208255</v>
+        <v>0.0004979677051587629</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.0009483884814213574</v>
+        <v>4.914338654237269e-06</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.04991239337760087</v>
+        <v>0.0007521917093370372</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.0009757568639190791</v>
+        <v>4.080261697073254e-06</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.0609790833218157</v>
+        <v>0.001133061783059252</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.00111857033290587</v>
+        <v>6.570933101265434e-06</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -3780,7 +3771,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -3792,7 +3783,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -3804,7 +3795,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
       <c r="AB26" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AC26" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -3816,7 +3807,7 @@
       </c>
       <c r="AE26" s="2" t="inlineStr"/>
       <c r="AF26" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AG26" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -3828,7 +3819,7 @@
       </c>
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -3848,7 +3839,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3857,43 +3848,43 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.01183039250203056</v>
+        <v>0.03580231620689336</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0008361303351472275</v>
+        <v>0.002063726442032366</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.02071552580492749</v>
+        <v>0.05074302287163481</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.001481611218138301</v>
+        <v>0.001669890073234396</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.03595530884220883</v>
+        <v>0.0718295784495116</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.00196261879723174</v>
+        <v>0.001998590746909841</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.007449404867875251</v>
+        <v>0.02429929226223913</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.0005164723724034511</v>
+        <v>0.001067358815104581</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.01028362590815869</v>
+        <v>0.02912279309908032</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.0006716957304179555</v>
+        <v>0.0009262872527034191</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.01410805920145593</v>
+        <v>0.03441961792674816</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.0007624090065221189</v>
+        <v>0.0009995414302262373</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -3905,7 +3896,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -3917,7 +3908,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -3929,7 +3920,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
       <c r="AB27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AC27" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -3941,7 +3932,7 @@
       </c>
       <c r="AE27" s="2" t="inlineStr"/>
       <c r="AF27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG27" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -3953,7 +3944,7 @@
       </c>
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -3973,7 +3964,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3982,43 +3973,43 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.01896362830931382</v>
+        <v>0.06046125070311605</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.001675812991538492</v>
+        <v>0.002270552850181354</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.03196337120466906</v>
+        <v>0.09263628916187981</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.002446836190030712</v>
+        <v>0.001817303782928136</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.05440680721602206</v>
+        <v>0.1366537957489053</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.002453409880191403</v>
+        <v>0.002338016448942837</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.01175069967550547</v>
+        <v>0.03958768789208255</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.00128369765736805</v>
+        <v>0.0009483884814213574</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.01592607308921117</v>
+        <v>0.04991239337760087</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.001515462623064492</v>
+        <v>0.0009757568639190791</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.02155184665138602</v>
+        <v>0.0609790833218157</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.001494454788703284</v>
+        <v>0.00111857033290587</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4030,7 +4021,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4042,7 +4033,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4054,7 +4045,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
       <c r="AB28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC28" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4066,7 +4057,7 @@
       </c>
       <c r="AE28" s="2" t="inlineStr"/>
       <c r="AF28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4078,7 +4069,7 @@
       </c>
       <c r="AI28" s="2" t="inlineStr"/>
       <c r="AJ28" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4098,7 +4089,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4107,43 +4098,43 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.02169232360473487</v>
+        <v>0.01183039250203056</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.0005071816242613565</v>
+        <v>0.0008361303351472275</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.03289596848985091</v>
+        <v>0.02071552580492749</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.001213517326006237</v>
+        <v>0.001481611218138301</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.05071692568506991</v>
+        <v>0.03595530884220883</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.002861468663446473</v>
+        <v>0.00196261879723174</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.01420954246556564</v>
+        <v>0.007449404867875251</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.0003545698484183353</v>
+        <v>0.0005164723724034511</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.01781388978347112</v>
+        <v>0.01028362590815869</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.0002681735460560363</v>
+        <v>0.0006716957304179555</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.02227144636633425</v>
+        <v>0.01410805920145593</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.0005574681611469983</v>
+        <v>0.0007624090065221189</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4155,7 +4146,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4167,7 +4158,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4179,7 +4170,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
       <c r="AB29" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC29" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4191,7 +4182,7 @@
       </c>
       <c r="AE29" s="2" t="inlineStr"/>
       <c r="AF29" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG29" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4203,7 +4194,7 @@
       </c>
       <c r="AI29" s="2" t="inlineStr"/>
       <c r="AJ29" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4223,7 +4214,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4232,43 +4223,43 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.006766421834070449</v>
+        <v>0.01896362830931382</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.001527204989275094</v>
+        <v>0.001675812991538492</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.01279077921471389</v>
+        <v>0.03196337120466906</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.002787481007421746</v>
+        <v>0.002446836190030712</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.02394058680230393</v>
+        <v>0.05440680721602206</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.003768989478208536</v>
+        <v>0.002453409880191403</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.004093792534802756</v>
+        <v>0.01175069967550547</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.0009929245939454619</v>
+        <v>0.00128369765736805</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.006016247868621834</v>
+        <v>0.01592607308921117</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.001379864020342312</v>
+        <v>0.001515462623064492</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.008808753055589355</v>
+        <v>0.02155184665138602</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.001615727470990511</v>
+        <v>0.001494454788703284</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4280,7 +4271,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4292,7 +4283,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4304,7 +4295,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC30" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4316,7 +4307,7 @@
       </c>
       <c r="AE30" s="2" t="inlineStr"/>
       <c r="AF30" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG30" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4328,7 +4319,7 @@
       </c>
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4348,7 +4339,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4357,43 +4348,43 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.04155173341620774</v>
+        <v>0.02169232360473487</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.00172869182725091</v>
+        <v>0.0005071816242613565</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.06475038809418446</v>
+        <v>0.03289596848985091</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.002196748580976563</v>
+        <v>0.001213517326006237</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.09705172419425907</v>
+        <v>0.05071692568506991</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.002935882612746689</v>
+        <v>0.002861468663446473</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.02644052575957629</v>
+        <v>0.01420954246556564</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.00113120251180514</v>
+        <v>0.0003545698484183353</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.03390302534819174</v>
+        <v>0.01781388978347112</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.001204193784263032</v>
+        <v>0.0002681735460560363</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.04201592968435603</v>
+        <v>0.02227144636633425</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.001168960427589778</v>
+        <v>0.0005574681611469983</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4405,7 +4396,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4417,7 +4408,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4429,7 +4420,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AC31" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4441,7 +4432,7 @@
       </c>
       <c r="AE31" s="2" t="inlineStr"/>
       <c r="AF31" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG31" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4453,7 +4444,7 @@
       </c>
       <c r="AI31" s="2" t="inlineStr"/>
       <c r="AJ31" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4473,7 +4464,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4482,43 +4473,43 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.03022135354969982</v>
+        <v>0.006766421834070449</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.001566913582754239</v>
+        <v>0.001527204989275094</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.04482870690982779</v>
+        <v>0.01279077921471389</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.001772954486312335</v>
+        <v>0.002787481007421746</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.06663824421500507</v>
+        <v>0.02394058680230393</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.001981869109278862</v>
+        <v>0.003768989478208536</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.01976438524092976</v>
+        <v>0.004093792534802756</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.001081040490767887</v>
+        <v>0.0009929245939454619</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.02445392035996143</v>
+        <v>0.006016247868621834</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.001125464911610024</v>
+        <v>0.001379864020342312</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>0.02991801049973425</v>
+        <v>0.008808753055589355</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>0.001135926525189758</v>
+        <v>0.001615727470990511</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4530,7 +4521,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4542,7 +4533,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4554,7 +4545,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
       <c r="AB32" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AC32" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4566,7 +4557,7 @@
       </c>
       <c r="AE32" s="2" t="inlineStr"/>
       <c r="AF32" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG32" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4578,7 +4569,7 @@
       </c>
       <c r="AI32" s="2" t="inlineStr"/>
       <c r="AJ32" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4598,7 +4589,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4607,43 +4598,43 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.02482420817002686</v>
+        <v>0.04155173341620774</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.001908967967903388</v>
+        <v>0.00172869182725091</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.04226304450191219</v>
+        <v>0.06475038809418446</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.003722563066060691</v>
+        <v>0.002196748580976563</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.07021270583212623</v>
+        <v>0.09705172419425907</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.008655012792139876</v>
+        <v>0.002935882612746689</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.01560427344283098</v>
+        <v>0.02644052575957629</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.0006566093764399087</v>
+        <v>0.00113120251180514</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.02119751216959605</v>
+        <v>0.03390302534819174</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>0.001220976421506521</v>
+        <v>0.001204193784263032</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.02820426111467891</v>
+        <v>0.04201592968435603</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>0.002488330934712589</v>
+        <v>0.001168960427589778</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4655,7 +4646,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4667,7 +4658,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4679,7 +4670,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC33" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4691,7 +4682,7 @@
       </c>
       <c r="AE33" s="2" t="inlineStr"/>
       <c r="AF33" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG33" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4703,7 +4694,7 @@
       </c>
       <c r="AI33" s="2" t="inlineStr"/>
       <c r="AJ33" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4723,7 +4714,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4732,43 +4723,43 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.04161046375793859</v>
+        <v>0.01354605349335143</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.001477244937062274</v>
+        <v>0.001253224217502229</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.06263830246085983</v>
+        <v>0.02537784428225476</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.001917137687964336</v>
+        <v>0.002445314040758438</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.09332312916950554</v>
+        <v>0.04530343922717356</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.001386761982891638</v>
+        <v>0.003564048353333479</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.02714779633235656</v>
+        <v>0.008075063314439758</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.001310843778161051</v>
+        <v>0.0008308732230982977</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.03388837500907407</v>
+        <v>0.01183902001613428</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0.001465745606975557</v>
+        <v>0.001127454966766457</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.04162390236898737</v>
+        <v>0.01683195767399901</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.0009533659926645374</v>
+        <v>0.001107344792943321</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>0.06046125070311605</v>
@@ -4778,11 +4769,9 @@
           <t>DropoutNet</t>
         </is>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>-0.3117829473581486</v>
-      </c>
+      <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>0.09263628916187981</v>
@@ -4792,11 +4781,9 @@
           <t>DropoutNet</t>
         </is>
       </c>
-      <c r="W34" s="3" t="n">
-        <v>-0.3238254357166572</v>
-      </c>
+      <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>0.1366537957489053</v>
@@ -4806,11 +4793,9 @@
           <t>DropoutNet</t>
         </is>
       </c>
-      <c r="AA34" s="3" t="n">
-        <v>-0.3170835200144589</v>
-      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
       <c r="AB34" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC34" s="3" t="n">
         <v>0.03958768789208255</v>
@@ -4820,11 +4805,9 @@
           <t>DropoutNet</t>
         </is>
       </c>
-      <c r="AE34" s="3" t="n">
-        <v>-0.3142363755528633</v>
-      </c>
+      <c r="AE34" s="2" t="inlineStr"/>
       <c r="AF34" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG34" s="3" t="n">
         <v>0.04991239337760087</v>
@@ -4834,11 +4817,9 @@
           <t>DropoutNet</t>
         </is>
       </c>
-      <c r="AI34" s="3" t="n">
-        <v>-0.3210428770125435</v>
-      </c>
+      <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>0.0609790833218157</v>
@@ -4848,12 +4829,397 @@
           <t>DropoutNet</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="n">
+      <c r="AM34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>USIM</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2025,2026,2027</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0.03022135354969982</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.001566913582754239</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.04482870690982779</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.001772954486312335</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.06663824421500507</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.001981869109278862</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.01976438524092976</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.001081040490767887</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.02445392035996143</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.001125464911610024</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0.02991801049973425</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>0.001135926525189758</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>0.06046125070311605</v>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>0.09263628916187981</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>0.1366537957489053</v>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3" t="n">
+        <v>0.03958768789208255</v>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3" t="n">
+        <v>0.04991239337760087</v>
+      </c>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>0.0609790833218157</v>
+      </c>
+      <c r="AL35" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2025,2026,2027</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.02482420817002686</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.001908967967903388</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.04226304450191219</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.003722563066060691</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.07021270583212623</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.008655012792139876</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.01560427344283098</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.0006566093764399087</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.02119751216959605</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0.001220976421506521</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0.02820426111467891</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.002488330934712589</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0.06046125070311605</v>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>0.09263628916187981</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>0.1366537957489053</v>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC36" s="3" t="n">
+        <v>0.03958768789208255</v>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG36" s="3" t="n">
+        <v>0.04991239337760087</v>
+      </c>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>0.0609790833218157</v>
+      </c>
+      <c r="AL36" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>CKG-RL</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2025,2026,2027</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0.04161046375793859</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.001477244937062274</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.06263830246085983</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.001917137687964336</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.09332312916950554</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0.001386761982891638</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.02714779633235656</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.001310843778161051</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.03388837500907407</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0.001465745606975557</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0.04162390236898737</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0.0009533659926645374</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>0.06046125070311605</v>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>-0.3117829473581486</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>0.09263628916187981</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>-0.3238254357166572</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>0.1366537957489053</v>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="n">
+        <v>-0.3170835200144589</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC37" s="3" t="n">
+        <v>0.03958768789208255</v>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AE37" s="3" t="n">
+        <v>-0.3142363755528633</v>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG37" s="3" t="n">
+        <v>0.04991239337760087</v>
+      </c>
+      <c r="AH37" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AI37" s="3" t="n">
+        <v>-0.3210428770125435</v>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>0.0609790833218157</v>
+      </c>
+      <c r="AL37" s="2" t="inlineStr">
+        <is>
+          <t>DropoutNet</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="n">
         <v>-0.3174068860740627</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM34"/>
+  <autoFilter ref="A1:AM37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4864,14 +5230,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -5900,31 +6266,31 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2025\aldi_official_wsl_gpu_rerun_gate_20260717_192714\per_item_full_cold_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2025\aldi_official_wsl_gpu_rerun_gate_20260717_192714\per_item_full_hot_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.4399722553286863</v>
+        <v>0.12614181717642</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4801781512784394</v>
+        <v>0.1639968994338822</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.5214728898379688</v>
+        <v>0.2122516086304752</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.3707885957182274</v>
+        <v>0.09401705637723326</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.3837888534149859</v>
+        <v>0.1062041785433139</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3942288549707709</v>
+        <v>0.1183265612923325</v>
       </c>
     </row>
     <row r="18">
@@ -5960,31 +6326,31 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2026\aldi_official_wsl_gpu_rerun_gate_20260717_203453\per_item_full_cold_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2026\aldi_official_wsl_gpu_rerun_gate_20260717_203453\per_item_full_hot_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.455450567243436</v>
+        <v>0.1349064511201797</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5002026870742468</v>
+        <v>0.1708011778552557</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.5417958443198959</v>
+        <v>0.2210844600439146</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.3826429066345881</v>
+        <v>0.1024064376798182</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.3971737042792708</v>
+        <v>0.1139617827073767</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.407717305764997</v>
+        <v>0.1266227216400013</v>
       </c>
     </row>
     <row r="19">
@@ -6020,31 +6386,31 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2027\aldi_official_wsl_gpu_rerun_gate_20260717_205646\per_item_full_cold_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2027\aldi_official_wsl_gpu_rerun_gate_20260717_205646\per_item_full_hot_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.4652876115681961</v>
+        <v>0.1538397722823481</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.5099125097780239</v>
+        <v>0.1954055883534992</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.5521278725234352</v>
+        <v>0.2431864222908143</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.3887442115832776</v>
+        <v>0.1163863386842875</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>0.4032738113722385</v>
+        <v>0.1296778832685914</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.4139647726090377</v>
+        <v>0.14171471092709</v>
       </c>
     </row>
     <row r="20">
@@ -6415,7 +6781,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -6426,45 +6792,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
         <v>68</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="3" t="n">
-        <v>0.1034615581666464</v>
+        <v>0.0251347031516868</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.1427673345710348</v>
+        <v>0.06225125154268782</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.1906413781535744</v>
+        <v>0.1118597472130274</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.07520520077464966</v>
+        <v>0.0152533245915373</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.08793359630661106</v>
+        <v>0.02694029585339541</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.09997131587094285</v>
+        <v>0.03941776121599404</v>
       </c>
     </row>
     <row r="27">
@@ -6475,7 +6841,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -6486,45 +6852,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
         <v>68</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="3" t="n">
-        <v>0.1137262127253801</v>
+        <v>0.03206210607662479</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1562374620617979</v>
+        <v>0.05436008596318311</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.2116346676283192</v>
+        <v>0.1024040058943937</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.08202797171125485</v>
+        <v>0.0196968420304419</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.09581111620102307</v>
+        <v>0.02684256037918414</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.1096894866353944</v>
+        <v>0.03875188723752332</v>
       </c>
     </row>
     <row r="28">
@@ -6535,7 +6901,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -6546,45 +6912,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
         <v>68</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="3" t="n">
-        <v>0.1236100988489956</v>
+        <v>0.01503636499440224</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.1661936702904296</v>
+        <v>0.03931020062854771</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.2339013676999954</v>
+        <v>0.08481759132359083</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.08908165873714494</v>
+        <v>0.008423276826784943</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.1027316368965699</v>
+        <v>0.01629736444842986</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.1198426640269678</v>
+        <v>0.02760666013962692</v>
       </c>
     </row>
     <row r="29">
@@ -6595,7 +6961,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -6620,31 +6986,31 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.1781838407414267</v>
+        <v>0.1034615581666464</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.238666386159201</v>
+        <v>0.1427673345710348</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.3183647553766217</v>
+        <v>0.1906413781535744</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.1284423440163387</v>
+        <v>0.07520520077464966</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.1479698282448617</v>
+        <v>0.08793359630661106</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.1680626658859776</v>
+        <v>0.09997131587094285</v>
       </c>
     </row>
     <row r="30">
@@ -6655,7 +7021,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -6680,31 +7046,31 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.1850094910608845</v>
+        <v>0.1137262127253801</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.246055299954774</v>
+        <v>0.1562374620617979</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.328989930694398</v>
+        <v>0.2116346676283192</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.1327726286404353</v>
+        <v>0.08202797171125485</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.1524320080632644</v>
+        <v>0.09581111620102307</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.1732433499844614</v>
+        <v>0.1096894866353944</v>
       </c>
     </row>
     <row r="31">
@@ -6715,7 +7081,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -6740,31 +7106,31 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.2006931760598949</v>
+        <v>0.1236100988489956</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.2658308942199011</v>
+        <v>0.1661936702904296</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.3510729580142337</v>
+        <v>0.2339013676999954</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1427946684650289</v>
+        <v>0.08908165873714494</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.1638863574837198</v>
+        <v>0.1027316368965699</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.1852876373532723</v>
+        <v>0.1198426640269678</v>
       </c>
     </row>
     <row r="32">
@@ -6775,7 +7141,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -6800,31 +7166,31 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.09105883073286326</v>
+        <v>0.1781838407414267</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1457718762342224</v>
+        <v>0.238666386159201</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.2185494683051646</v>
+        <v>0.3183647553766217</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>0.06266462104421658</v>
+        <v>0.1284423440163387</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>0.08035662373915219</v>
+        <v>0.1479698282448617</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.09866524593137309</v>
+        <v>0.1680626658859776</v>
       </c>
     </row>
     <row r="33">
@@ -6835,7 +7201,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -6860,31 +7226,31 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.101725479526753</v>
+        <v>0.1850094910608845</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1504240840287636</v>
+        <v>0.246055299954774</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>0.2241767365334062</v>
+        <v>0.328989930694398</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.06841230353097956</v>
+        <v>0.1327726286404353</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>0.08403816761827279</v>
+        <v>0.1524320080632644</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.1025433980040861</v>
+        <v>0.1732433499844614</v>
       </c>
     </row>
     <row r="34">
@@ -6895,7 +7261,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -6920,42 +7286,42 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2027\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2027\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\content_delta_pop5\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.1201111570045485</v>
+        <v>0.2006931760598949</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1741658431821256</v>
+        <v>0.2658308942199011</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0.2518567979592535</v>
+        <v>0.3510729580142337</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.08215148811294601</v>
+        <v>0.1427946684650289</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.09942550605389025</v>
+        <v>0.1638863574837198</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.1190112809896811</v>
+        <v>0.1852876373532723</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Junyi</t>
+          <t>MOOCCube</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -6973,49 +7339,49 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\popularity_compare\per_item_full_cold_popularity_static.csv</t>
+          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\popularity_compare\popularity_static_result.json</t>
+          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.016577417605997</v>
+        <v>0.09105883073286326</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.02924837170854573</v>
+        <v>0.1457718762342224</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0.05249153373433282</v>
+        <v>0.2185494683051646</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.01040151924197901</v>
+        <v>0.06266462104421658</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0.01444327501349325</v>
+        <v>0.08035662373915219</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.02030144819010495</v>
+        <v>0.09866524593137309</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Junyi</t>
+          <t>MOOCCube</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -7033,49 +7399,49 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\popularity_compare_strictfix\per_item_full_cold_popularity_static.csv</t>
+          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\popularity_compare_strictfix\popularity_static_result.json</t>
+          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.01648658302641791</v>
+        <v>0.101725479526753</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.02912189743029851</v>
+        <v>0.1504240840287636</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.05131017031313433</v>
+        <v>0.2241767365334062</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.01006356083044776</v>
+        <v>0.06841230353097956</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.01410539558119403</v>
+        <v>0.08403816761827279</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.01969126360223881</v>
+        <v>0.1025433980040861</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Junyi</t>
+          <t>MOOCCube</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -7093,38 +7459,38 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\popularity_compare_strictfix\per_item_full_cold_popularity_static.csv</t>
+          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2027\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\popularity_compare_strictfix\popularity_static_result.json</t>
+          <t>outputs\significance_per_item_exports\mooccube\ckg_rl_full\strict_item_cold_balanced_thr1_seed_2027\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0.01618731348699552</v>
+        <v>0.1201111570045485</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.02756892046786249</v>
+        <v>0.1741658431821256</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.05188732844813154</v>
+        <v>0.2518567979592535</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.009833266811061286</v>
+        <v>0.08215148811294601</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.01346312395067265</v>
+        <v>0.09942550605389025</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.01957776020926756</v>
+        <v>0.1190112809896811</v>
       </c>
     </row>
     <row r="38">
@@ -7135,7 +7501,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -7160,31 +7526,31 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\bpr_compare\per_item_full_cold_bpr_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\popularity_compare\per_item_full_cold_popularity_static.csv</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\bpr_compare\bpr_static_result.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\popularity_compare\popularity_static_result.json</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1277635463788047</v>
+        <v>0.016577417605997</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1816866650038043</v>
+        <v>0.02924837170854573</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>0.2589571665558293</v>
+        <v>0.05249153373433282</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0.08799998145204306</v>
+        <v>0.01040151924197901</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>0.1053573390052262</v>
+        <v>0.01444327501349325</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.1247853419768706</v>
+        <v>0.02030144819010495</v>
       </c>
     </row>
     <row r="39">
@@ -7195,7 +7561,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -7220,31 +7586,31 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\bpr_compare_strictfix\per_item_full_cold_bpr_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\popularity_compare_strictfix\per_item_full_cold_popularity_static.csv</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\bpr_compare_strictfix\bpr_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\popularity_compare_strictfix\popularity_static_result.json</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.1239876822664166</v>
+        <v>0.01648658302641791</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1767041639160843</v>
+        <v>0.02912189743029851</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>0.2544094492619012</v>
+        <v>0.05131017031313433</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.08630779673608782</v>
+        <v>0.01006356083044776</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>0.1032873271745374</v>
+        <v>0.01410539558119403</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.1228515582331215</v>
+        <v>0.01969126360223881</v>
       </c>
     </row>
     <row r="40">
@@ -7255,7 +7621,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -7280,31 +7646,31 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\bpr_compare_strictfix\per_item_full_cold_bpr_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\popularity_compare_strictfix\per_item_full_cold_popularity_static.csv</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\bpr_compare_strictfix\bpr_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\popularity_compare_strictfix\popularity_static_result.json</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1357576542235593</v>
+        <v>0.01618731348699552</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1908318599099011</v>
+        <v>0.02756892046786249</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0.271210823734565</v>
+        <v>0.05188732844813154</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.09390778210048732</v>
+        <v>0.009833266811061286</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0.1116013364771038</v>
+        <v>0.01346312395067265</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.1317915981197037</v>
+        <v>0.01957776020926756</v>
       </c>
     </row>
     <row r="41">
@@ -7315,7 +7681,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -7340,31 +7706,31 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\dropoutnet_compare\per_item_full_cold_dropoutnet_official_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\bpr_compare\per_item_full_cold_bpr_static.csv</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\dropoutnet_compare\dropoutnet_official_static_result.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\bpr_compare\bpr_static_result.json</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.07445781649623553</v>
+        <v>0.1277635463788047</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.1274155621404102</v>
+        <v>0.1816866650038043</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.212850055700113</v>
+        <v>0.2589571665558293</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0.04589783127749353</v>
+        <v>0.08799998145204306</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0.06288730417842878</v>
+        <v>0.1053573390052262</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.08435816198976666</v>
+        <v>0.1247853419768706</v>
       </c>
     </row>
     <row r="42">
@@ -7375,7 +7741,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -7400,31 +7766,31 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\dropoutnet_compare_strictfix\per_item_full_cold_dropoutnet_official_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\bpr_compare_strictfix\per_item_full_cold_bpr_static.csv</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\dropoutnet_compare_strictfix\dropoutnet_official_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\bpr_compare_strictfix\bpr_static_result.json</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.07252514958502369</v>
+        <v>0.1239876822664166</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1226973785232139</v>
+        <v>0.1767041639160843</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>0.2004507794262732</v>
+        <v>0.2544094492619012</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.04595256344228472</v>
+        <v>0.08630779673608782</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>0.06204599303741769</v>
+        <v>0.1032873271745374</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.0815426161028302</v>
+        <v>0.1228515582331215</v>
       </c>
     </row>
     <row r="43">
@@ -7435,7 +7801,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -7460,31 +7826,31 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\dropoutnet_compare_strictfix\per_item_full_cold_dropoutnet_official_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\bpr_compare_strictfix\per_item_full_cold_bpr_static.csv</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\dropoutnet_compare_strictfix\dropoutnet_official_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\bpr_compare_strictfix\bpr_static_result.json</t>
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.07638125249108821</v>
+        <v>0.1357576542235593</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.131569906608244</v>
+        <v>0.1908318599099011</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>0.2155743999663616</v>
+        <v>0.271210823734565</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>0.04729722798242754</v>
+        <v>0.09390778210048732</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>0.06495648499892262</v>
+        <v>0.1116013364771038</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.08602292832842726</v>
+        <v>0.1317915981197037</v>
       </c>
     </row>
     <row r="44">
@@ -7495,7 +7861,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -7520,31 +7886,31 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\lightgcn_compare\per_item_full_cold_lightgcn_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\dropoutnet_compare\per_item_full_cold_dropoutnet_official_static.csv</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\lightgcn_compare\lightgcn_static_result.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\dropoutnet_compare\dropoutnet_official_static_result.json</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.1449637338693505</v>
+        <v>0.07445781649623553</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2238806312800092</v>
+        <v>0.1274155621404102</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>0.3382438018596767</v>
+        <v>0.212850055700113</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>0.09542915245228428</v>
+        <v>0.04589783127749353</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>0.1207432878653084</v>
+        <v>0.06288730417842878</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0.1495526456320927</v>
+        <v>0.08435816198976666</v>
       </c>
     </row>
     <row r="45">
@@ -7555,7 +7921,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -7580,31 +7946,31 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\lightgcn_compare_strictfix\per_item_full_cold_lightgcn_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\dropoutnet_compare_strictfix\per_item_full_cold_dropoutnet_official_static.csv</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\lightgcn_compare_strictfix\lightgcn_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\dropoutnet_compare_strictfix\dropoutnet_official_static_result.json</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.1157876368833163</v>
+        <v>0.07252514958502369</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1872474267382812</v>
+        <v>0.1226973785232139</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>0.291041089509831</v>
+        <v>0.2004507794262732</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>0.07513789719696962</v>
+        <v>0.04595256344228472</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>0.09806366719740595</v>
+        <v>0.06204599303741769</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.124126857611892</v>
+        <v>0.0815426161028302</v>
       </c>
     </row>
     <row r="46">
@@ -7615,7 +7981,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -7640,31 +8006,31 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\lightgcn_compare_strictfix\per_item_full_cold_lightgcn_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\dropoutnet_compare_strictfix\per_item_full_cold_dropoutnet_official_static.csv</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\lightgcn_compare_strictfix\lightgcn_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\dropoutnet_compare_strictfix\dropoutnet_official_static_result.json</t>
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1407927704845442</v>
+        <v>0.07638125249108821</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.2227844563403626</v>
+        <v>0.131569906608244</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>0.3411211597597884</v>
+        <v>0.2155743999663616</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.09325988704455083</v>
+        <v>0.04729722798242754</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>0.1195448245463726</v>
+        <v>0.06495648499892262</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.1492869956014555</v>
+        <v>0.08602292832842726</v>
       </c>
     </row>
     <row r="47">
@@ -7675,7 +8041,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -7700,31 +8066,31 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\ccfcrec_compare\per_item_full_cold_ccfcrec_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\lightgcn_compare\per_item_full_cold_lightgcn_static.csv</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\ccfcrec_compare\ccfcrec_static_result.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\lightgcn_compare\lightgcn_static_result.json</t>
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.0182358434969882</v>
+        <v>0.1449637338693505</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.0303412889150965</v>
+        <v>0.2238806312800092</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>0.05989874990432496</v>
+        <v>0.3382438018596767</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>0.01171770640804114</v>
+        <v>0.09542915245228428</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>0.01556695827581277</v>
+        <v>0.1207432878653084</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>0.02287625891407593</v>
+        <v>0.1495526456320927</v>
       </c>
     </row>
     <row r="48">
@@ -7735,7 +8101,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -7760,31 +8126,31 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\ccfcrec_compare_strictfix\per_item_full_cold_ccfcrec_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\lightgcn_compare_strictfix\per_item_full_cold_lightgcn_static.csv</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\ccfcrec_compare_strictfix\ccfcrec_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\lightgcn_compare_strictfix\lightgcn_static_result.json</t>
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.01492624739527411</v>
+        <v>0.1157876368833163</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.02555474397077416</v>
+        <v>0.1872474267382812</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.06223605688976962</v>
+        <v>0.291041089509831</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.009558950540079433</v>
+        <v>0.07513789719696962</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.01293727457055054</v>
+        <v>0.09806366719740595</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.02198543808113926</v>
+        <v>0.124126857611892</v>
       </c>
     </row>
     <row r="49">
@@ -7795,7 +8161,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -7820,31 +8186,31 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\ccfcrec_compare_strictfix\per_item_full_cold_ccfcrec_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\lightgcn_compare_strictfix\per_item_full_cold_lightgcn_static.csv</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\ccfcrec_compare_strictfix\ccfcrec_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\lightgcn_compare_strictfix\lightgcn_static_result.json</t>
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.01625015335183699</v>
+        <v>0.1407927704845442</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.02830478869141888</v>
+        <v>0.2227844563403626</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>0.06242709074887758</v>
+        <v>0.3411211597597884</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>0.01057492534155157</v>
+        <v>0.09325988704455083</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>0.01444134472302422</v>
+        <v>0.1195448245463726</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>0.02286914066844347</v>
+        <v>0.1492869956014555</v>
       </c>
     </row>
     <row r="50">
@@ -7855,7 +8221,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -7880,31 +8246,31 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\aldi_compare\per_item_full_cold_aldi_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\ccfcrec_compare\per_item_full_cold_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\aldi_compare\aldi_static_result.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\ccfcrec_compare\ccfcrec_static_result.json</t>
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.1160042240637378</v>
+        <v>0.0182358434969882</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1860150351363388</v>
+        <v>0.0303412889150965</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>0.2953725251017923</v>
+        <v>0.05989874990432496</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0.07524298991786575</v>
+        <v>0.01171770640804114</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>0.0976424809564431</v>
+        <v>0.01556695827581277</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>0.1251306121849307</v>
+        <v>0.02287625891407593</v>
       </c>
     </row>
     <row r="51">
@@ -7915,7 +8281,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -7940,31 +8306,31 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\aldi_compare_strictfix\per_item_full_cold_aldi_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\ccfcrec_compare_strictfix\per_item_full_cold_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\aldi_compare_strictfix\aldi_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\ccfcrec_compare_strictfix\ccfcrec_static_result.json</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.1107392274168879</v>
+        <v>0.01492624739527411</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1774742940845673</v>
+        <v>0.02555474397077416</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0.2835517164905929</v>
+        <v>0.06223605688976962</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.07154115920062315</v>
+        <v>0.009558950540079433</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0.09291618720665701</v>
+        <v>0.01293727457055054</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>0.1195687352822337</v>
+        <v>0.02198543808113926</v>
       </c>
     </row>
     <row r="52">
@@ -7975,7 +8341,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -8000,31 +8366,31 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\aldi_compare_strictfix\per_item_full_cold_aldi_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\ccfcrec_compare_strictfix\per_item_full_cold_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\aldi_compare_strictfix\aldi_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\ccfcrec_compare_strictfix\ccfcrec_static_result.json</t>
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.1204815566574285</v>
+        <v>0.01625015335183699</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1929265182631824</v>
+        <v>0.02830478869141888</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>0.301578496821211</v>
+        <v>0.06242709074887758</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>0.07777387998368872</v>
+        <v>0.01057492534155157</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>0.1010231385874092</v>
+        <v>0.01444134472302422</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>0.128307099986094</v>
+        <v>0.02286914066844347</v>
       </c>
     </row>
     <row r="53">
@@ -8035,7 +8401,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -8049,7 +8415,7 @@
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>direct_all_item_macro_validated</t>
+          <t>cold_hot_course_count_weighted</t>
         </is>
       </c>
       <c r="G53" s="2" t="n">
@@ -8060,31 +8426,31 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2025_relationfix_lr1e-6_p8_trainonly\kgrec_strict_adapter_report.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\aldi_compare\per_item_full_cold_aldi_static.csv</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2025_relationfix_lr1e-6_p8_trainonly\kgrec_strict_adapter_report.json</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\aldi_compare\aldi_static_result.json</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.02557418636607475</v>
+        <v>0.1160042240637378</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.04714759981417041</v>
+        <v>0.1860150351363388</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0.08514164273948728</v>
+        <v>0.2953725251017923</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0.01502422251395991</v>
+        <v>0.07524298991786575</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>0.02195263649294227</v>
+        <v>0.0976424809564431</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>0.0314699647280805</v>
+        <v>0.1251306121849307</v>
       </c>
     </row>
     <row r="54">
@@ -8095,7 +8461,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -8109,7 +8475,7 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>direct_all_item_macro_validated</t>
+          <t>cold_hot_course_count_weighted</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -8120,31 +8486,31 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2026_relationfix_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\aldi_compare_strictfix\per_item_full_cold_aldi_static.csv</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2026_relationfix_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\aldi_compare_strictfix\aldi_static_result.json</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.03809407865803967</v>
+        <v>0.1107392274168879</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.06612409968608979</v>
+        <v>0.1774742940845673</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>0.1090603263583582</v>
+        <v>0.2835517164905929</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>0.02382826899375561</v>
+        <v>0.07154115920062315</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>0.0328356980270461</v>
+        <v>0.09291618720665701</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>0.04365164754809246</v>
+        <v>0.1195687352822337</v>
       </c>
     </row>
     <row r="55">
@@ -8155,7 +8521,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -8169,7 +8535,7 @@
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>direct_all_item_macro_validated</t>
+          <t>cold_hot_course_count_weighted</t>
         </is>
       </c>
       <c r="G55" s="2" t="n">
@@ -8180,31 +8546,31 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2027_main_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\aldi_compare_strictfix\per_item_full_cold_aldi_static.csv</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2027_main_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\aldi_compare_strictfix\aldi_static_result.json</t>
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.03103940743482226</v>
+        <v>0.1204815566574285</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.05423506220832437</v>
+        <v>0.1929265182631824</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>0.09287482372592462</v>
+        <v>0.301578496821211</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>0.01883549347020313</v>
+        <v>0.07777387998368872</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>0.02626806293995019</v>
+        <v>0.1010231385874092</v>
       </c>
       <c r="P55" s="3" t="n">
-        <v>0.03596176857777174</v>
+        <v>0.128307099986094</v>
       </c>
     </row>
     <row r="56">
@@ -8215,7 +8581,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -8229,7 +8595,7 @@
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>direct_all_item_macro_validated</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
@@ -8240,31 +8606,31 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\cgrc_paper_compare\per_item_full_cold_cgrc_paper_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2025_relationfix_lr1e-6_p8_trainonly\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\cgrc_paper_compare\per_item_full_hot_cgrc_paper_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2025_relationfix_lr1e-6_p8_trainonly\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.1506225919880255</v>
+        <v>0.02557418636607475</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.2200708376527489</v>
+        <v>0.04714759981417041</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.3127508835493087</v>
+        <v>0.08514164273948728</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.100536252012286</v>
+        <v>0.01502422251395991</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.1227893579361212</v>
+        <v>0.02195263649294227</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.1460735139438652</v>
+        <v>0.0314699647280805</v>
       </c>
     </row>
     <row r="57">
@@ -8275,7 +8641,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -8289,7 +8655,7 @@
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>direct_all_item_macro_validated</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -8300,31 +8666,31 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\cgrc_paper_compare_strictfix\per_item_full_cold_cgrc_paper_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2026_relationfix_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\cgrc_paper_compare_strictfix\per_item_full_hot_cgrc_paper_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2026_relationfix_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.1432627074164766</v>
+        <v>0.03809407865803967</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.2091070434073992</v>
+        <v>0.06612409968608979</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0.2966697513653561</v>
+        <v>0.1090603263583582</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0.09718667401016837</v>
+        <v>0.02382826899375561</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0.1182644069523427</v>
+        <v>0.0328356980270461</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0.140286106300255</v>
+        <v>0.04365164754809246</v>
       </c>
     </row>
     <row r="58">
@@ -8335,7 +8701,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -8349,7 +8715,7 @@
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>direct_all_item_macro_validated</t>
         </is>
       </c>
       <c r="G58" s="2" t="n">
@@ -8360,31 +8726,31 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\cgrc_paper_compare_strictfix\per_item_full_cold_cgrc_paper_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2027_main_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\cgrc_paper_compare_strictfix\per_item_full_hot_cgrc_paper_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\junyi_seed2027_main_lr1e-6_p8\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.1507502662111637</v>
+        <v>0.03103940743482226</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.2219082924190978</v>
+        <v>0.05423506220832437</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>0.3141294583184033</v>
+        <v>0.09287482372592462</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>0.1017686001530105</v>
+        <v>0.01883549347020313</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>0.1247247137157546</v>
+        <v>0.02626806293995019</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>0.1480072897443349</v>
+        <v>0.03596176857777174</v>
       </c>
     </row>
     <row r="59">
@@ -8395,7 +8761,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -8420,31 +8786,31 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\cgrc_paper_compare\per_item_full_cold_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+          <t>outputs\junyi\official_prereq_seed2025\strict_item_cold_balanced_thr1_seed_2025\cgrc_paper_compare\per_item_full_hot_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.1244836805475901</v>
+        <v>0.1506225919880255</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1947944575301518</v>
+        <v>0.2200708376527489</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>0.2935979526385972</v>
+        <v>0.3127508835493087</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>0.08187733966154374</v>
+        <v>0.100536252012286</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>0.1044757301636542</v>
+        <v>0.1227893579361212</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>0.1293359230248696</v>
+        <v>0.1460735139438652</v>
       </c>
     </row>
     <row r="60">
@@ -8455,7 +8821,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -8480,31 +8846,31 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\cgrc_paper_compare_strictfix\per_item_full_cold_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\cgrc_paper_compare_strictfix\per_item_full_hot_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.1166075201931611</v>
+        <v>0.1432627074164766</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1869438016285049</v>
+        <v>0.2091070434073992</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>0.284251496260333</v>
+        <v>0.2966697513653561</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>0.07594033808531649</v>
+        <v>0.09718667401016837</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>0.09853221833915983</v>
+        <v>0.1182644069523427</v>
       </c>
       <c r="P60" s="3" t="n">
-        <v>0.1229890811587359</v>
+        <v>0.140286106300255</v>
       </c>
     </row>
     <row r="61">
@@ -8515,7 +8881,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -8540,31 +8906,31 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\cgrc_paper_compare_strictfix\per_item_full_cold_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\cgrc_paper_compare_strictfix\per_item_full_hot_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.1252394437325181</v>
+        <v>0.1507502662111637</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.2010401938796062</v>
+        <v>0.2219082924190978</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.3095632398630749</v>
+        <v>0.3141294583184033</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.08096010388856135</v>
+        <v>0.1017686001530105</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.1052722316470875</v>
+        <v>0.1247247137157546</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.1325223102629348</v>
+        <v>0.1480072897443349</v>
       </c>
     </row>
     <row r="62">
@@ -8575,7 +8941,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -8586,45 +8952,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
         <v>71</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="3" t="n">
-        <v>0.1432243882600482</v>
+        <v>0.04039911032071352</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.2283353977130058</v>
+        <v>0.08790424170875298</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>0.3436477040389199</v>
+        <v>0.1569145680568793</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>0.09089981631656936</v>
+        <v>0.02316372239001332</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>0.1181980105512442</v>
+        <v>0.03834302024784767</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>0.1471997605103965</v>
+        <v>0.05554557407757177</v>
       </c>
     </row>
     <row r="63">
@@ -8635,7 +9001,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -8646,45 +9012,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
         <v>71</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="3" t="n">
-        <v>0.1478038048922553</v>
+        <v>0.05279864739401549</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.2319595534351321</v>
+        <v>0.1024729569572007</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>0.3463193194557342</v>
+        <v>0.1733169180327174</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>0.09558016747644765</v>
+        <v>0.0300970399065477</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>0.1225943465981517</v>
+        <v>0.04598597226791548</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>0.1513199090170475</v>
+        <v>0.06377830532821768</v>
       </c>
     </row>
     <row r="64">
@@ -8695,7 +9061,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -8706,45 +9072,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
         <v>71</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="3" t="n">
-        <v>0.1068763534105687</v>
+        <v>0.04283308620385778</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1738078465500227</v>
+        <v>0.07880763326159881</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0.2736654139755844</v>
+        <v>0.1463812515372949</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0.06660162332405056</v>
+        <v>0.024910178550486</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0.08805571705829215</v>
+        <v>0.03640083315471509</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0.1131668688164282</v>
+        <v>0.05330010681867861</v>
       </c>
     </row>
     <row r="65">
@@ -8755,7 +9121,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -8780,31 +9146,31 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.09816190330789869</v>
+        <v>0.1244836805475901</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.1757694797972933</v>
+        <v>0.1947944575301518</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>0.2920497115863896</v>
+        <v>0.2935979526385972</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>0.05875692368276997</v>
+        <v>0.08187733966154374</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>0.08364341495647787</v>
+        <v>0.1044757301636542</v>
       </c>
       <c r="P65" s="3" t="n">
-        <v>0.1128771405063178</v>
+        <v>0.1293359230248696</v>
       </c>
     </row>
     <row r="66">
@@ -8815,7 +9181,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -8840,31 +9206,31 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.0840096720851521</v>
+        <v>0.1166075201931611</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.1511942954773071</v>
+        <v>0.1869438016285049</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0.2667119220038677</v>
+        <v>0.284251496260333</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.05057595008890518</v>
+        <v>0.07594033808531649</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.07201288499080974</v>
+        <v>0.09853221833915983</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>0.1009326514046475</v>
+        <v>0.1229890811587359</v>
       </c>
     </row>
     <row r="67">
@@ -8875,7 +9241,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>USIM</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -8900,42 +9266,42 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.09677960106477175</v>
+        <v>0.1252394437325181</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.1758192768462315</v>
+        <v>0.2010401938796062</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0.2898975604911442</v>
+        <v>0.3095632398630749</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0.05741096923606322</v>
+        <v>0.08096010388856135</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0.08275357722540561</v>
+        <v>0.1052722316470875</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0.1114148677099227</v>
+        <v>0.1325223102629348</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -8953,49 +9319,49 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>820</v>
+        <v>71</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>6083</v>
+        <v>596</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_popularity_static.csv</t>
+          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\popularity_static_result.json</t>
+          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.0008242609518615095</v>
+        <v>0.1432243882600482</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.001625002380327394</v>
+        <v>0.2283353977130058</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.003118287939345213</v>
+        <v>0.3436477040389199</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.0004993930628132696</v>
+        <v>0.09089981631656936</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.0007537815144285094</v>
+        <v>0.1181980105512442</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.001125480131971607</v>
+        <v>0.1471997605103965</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -9013,49 +9379,49 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>819</v>
+        <v>71</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>5996</v>
+        <v>599</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_popularity_static.csv</t>
+          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\popularity_static_result.json</t>
+          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.0008218028737784299</v>
+        <v>0.1478038048922553</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.001621471929273661</v>
+        <v>0.2319595534351321</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>0.00317769444513573</v>
+        <v>0.3463193194557342</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0.0004924982426412326</v>
+        <v>0.09558016747644765</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>0.0007475558530887748</v>
+        <v>0.1225943465981517</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>0.001137109682347762</v>
+        <v>0.1513199090170475</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>SEMCo</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -9073,49 +9439,49 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>820</v>
+        <v>71</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>6065</v>
+        <v>598</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_popularity_static.csv</t>
+          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\popularity_static_result.json</t>
+          <t>outputs\junyi\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.0007924905144517066</v>
+        <v>0.1068763534105687</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.001582559873856209</v>
+        <v>0.1738078465500227</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0.003112922252360204</v>
+        <v>0.2736654139755844</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0.0005020118100217865</v>
+        <v>0.06660162332405056</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0.0007552377604938272</v>
+        <v>0.08805571705829215</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0.001136595534858388</v>
+        <v>0.1131668688164282</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -9133,49 +9499,49 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>820</v>
+        <v>71</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>6083</v>
+        <v>596</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_bpr_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\bpr_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2025\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.03423136457734318</v>
+        <v>0.09816190330789869</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.04892160222837896</v>
+        <v>0.1757694797972933</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.06966022273631754</v>
+        <v>0.2920497115863896</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.02346151891079241</v>
+        <v>0.05875692368276997</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0.0282022532777633</v>
+        <v>0.08364341495647787</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.03342529578736781</v>
+        <v>0.1128771405063178</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -9193,49 +9559,49 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>819</v>
+        <v>71</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>5996</v>
+        <v>599</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_bpr_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\bpr_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2026\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.03813958133106383</v>
+        <v>0.0840096720851521</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.05220177788754219</v>
+        <v>0.1511942954773071</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>0.07359600905884078</v>
+        <v>0.2667119220038677</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>0.02550103058347762</v>
+        <v>0.05057595008890518</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>0.03005472274148203</v>
+        <v>0.07201288499080974</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>0.03542429814198092</v>
+        <v>0.1009326514046475</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>Junyi</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>BPR</t>
+          <t>CKG-RL</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -9253,38 +9619,38 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>820</v>
+        <v>71</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>6065</v>
+        <v>598</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_bpr_static.csv</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\bpr_static_result.json</t>
+          <t>outputs\junyi\main_table_3seed\strict_item_cold_balanced_thr1_seed_2027\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.03503600271227306</v>
+        <v>0.09677960106477175</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.0511056884989833</v>
+        <v>0.1758192768462315</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>0.07223250355337646</v>
+        <v>0.2898975604911442</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>0.02393532729244735</v>
+        <v>0.05741096923606322</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>0.02911140327799564</v>
+        <v>0.08275357722540561</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>0.03440925985089575</v>
+        <v>0.1114148677099227</v>
       </c>
     </row>
     <row r="74">
@@ -9295,7 +9661,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -9320,31 +9686,31 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_drop_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_popularity_static.csv</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\drop_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\popularity_static_result.json</t>
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>0.0630790821351046</v>
+        <v>0.0008242609518615095</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.09415207610382895</v>
+        <v>0.001625002380327394</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>0.137103506396416</v>
+        <v>0.003118287939345213</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>0.04054916647123413</v>
+        <v>0.0004993930628132696</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>0.05050898258008223</v>
+        <v>0.0007537815144285094</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>0.06132183887789508</v>
+        <v>0.001125480131971607</v>
       </c>
     </row>
     <row r="75">
@@ -9355,7 +9721,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -9380,31 +9746,31 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_drop_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_popularity_static.csv</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\drop_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\popularity_static_result.json</t>
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.05927735174894303</v>
+        <v>0.0008218028737784299</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.09313513174092022</v>
+        <v>0.001621471929273661</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.1387342909767287</v>
+        <v>0.00317769444513573</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.03956094190429346</v>
+        <v>0.0004924982426412326</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.05044184417809747</v>
+        <v>0.0007475558530887748</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.06188617138062003</v>
+        <v>0.001137109682347762</v>
       </c>
     </row>
     <row r="76">
@@ -9415,7 +9781,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>DropoutNet</t>
+          <t>Popularity</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -9440,31 +9806,31 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_drop_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_popularity_static.csv</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\drop_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\popularity_static_result.json</t>
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.05902731822530054</v>
+        <v>0.0007924905144517066</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.09062165964089025</v>
+        <v>0.001582559873856209</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.1341235898735714</v>
+        <v>0.003112922252360204</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.03865295530072005</v>
+        <v>0.0005020118100217865</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.04878635337462293</v>
+        <v>0.0007552377604938272</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.05972923970693198</v>
+        <v>0.001136595534858388</v>
       </c>
     </row>
     <row r="77">
@@ -9475,7 +9841,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -9500,31 +9866,31 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_lightgcn_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_bpr_static.csv</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\lightgcn_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\bpr_static_result.json</t>
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.0113593675648047</v>
+        <v>0.03423136457734318</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.02106019518031796</v>
+        <v>0.04892160222837896</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>0.0370757964967008</v>
+        <v>0.06966022273631754</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>0.007139487250617969</v>
+        <v>0.02346151891079241</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>0.01024184757110515</v>
+        <v>0.0282022532777633</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>0.0142639934383736</v>
+        <v>0.03342529578736781</v>
       </c>
     </row>
     <row r="78">
@@ -9535,7 +9901,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -9560,31 +9926,31 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_lightgcn_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_bpr_static.csv</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\lightgcn_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\bpr_static_result.json</t>
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.01279577863692892</v>
+        <v>0.03813958133106383</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.02199442303114685</v>
+        <v>0.05220177788754219</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0.03710101141076361</v>
+        <v>0.07359600905884078</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0.008045619854184415</v>
+        <v>0.02550103058347762</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0.01097523564605582</v>
+        <v>0.03005472274148203</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0.01478044591855984</v>
+        <v>0.03542429814198092</v>
       </c>
     </row>
     <row r="79">
@@ -9595,7 +9961,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>LightGCN</t>
+          <t>BPR</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -9620,31 +9986,31 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_lightgcn_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_bpr_static.csv</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\lightgcn_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\bpr_static_result.json</t>
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.01133603130435804</v>
+        <v>0.03503600271227306</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01909195920331766</v>
+        <v>0.0511056884989833</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0.03368911861916206</v>
+        <v>0.07223250355337646</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0.007163107498823366</v>
+        <v>0.02393532729244735</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0.009633794507315111</v>
+        <v>0.02911140327799564</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>0.01327973824743435</v>
+        <v>0.03440925985089575</v>
       </c>
     </row>
     <row r="80">
@@ -9655,7 +10021,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -9680,31 +10046,31 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_ccfcrec_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_drop_static.csv</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_hot_ccfcrec_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\drop_static_result.json</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.01718943078544417</v>
+        <v>0.0630790821351046</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.0294331506901277</v>
+        <v>0.09415207610382895</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.05206270696187597</v>
+        <v>0.137103506396416</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.01028294250920723</v>
+        <v>0.04054916647123413</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.01422220406694061</v>
+        <v>0.05050898258008223</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.01989445609878848</v>
+        <v>0.06132183887789508</v>
       </c>
     </row>
     <row r="81">
@@ -9715,7 +10081,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -9740,31 +10106,31 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_ccfcrec_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_drop_static.csv</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_hot_ccfcrec_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\drop_static_result.json</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>0.02051969384346554</v>
+        <v>0.05927735174894303</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>0.03431728605950973</v>
+        <v>0.09313513174092022</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>0.0569565784829144</v>
+        <v>0.1387342909767287</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>0.01266387229401928</v>
+        <v>0.03956094190429346</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>0.01712333313967939</v>
+        <v>0.05044184417809747</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>0.0227966999897219</v>
+        <v>0.06188617138062003</v>
       </c>
     </row>
     <row r="82">
@@ -9775,7 +10141,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CCFCRec</t>
+          <t>DropoutNet</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -9800,31 +10166,31 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_ccfcrec_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_drop_static.csv</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_hot_ccfcrec_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\drop_static_result.json</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>0.01918176029903175</v>
+        <v>0.05902731822530054</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.03213967686436976</v>
+        <v>0.09062165964089025</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>0.05420113620327583</v>
+        <v>0.1341235898735714</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>0.01230528422328989</v>
+        <v>0.03865295530072005</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>0.01643268206101351</v>
+        <v>0.04878635337462293</v>
       </c>
       <c r="P82" s="3" t="n">
-        <v>0.02196438386564768</v>
+        <v>0.05972923970693198</v>
       </c>
     </row>
     <row r="83">
@@ -9835,7 +10201,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -9860,31 +10226,31 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_aldi_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_lightgcn_static.csv</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\aldi_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\lightgcn_static_result.json</t>
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0.02114193879579811</v>
+        <v>0.0113593675648047</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>0.03426005367789449</v>
+        <v>0.02106019518031796</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>0.0537412506413453</v>
+        <v>0.0370757964967008</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>0.01382981632459472</v>
+        <v>0.007139487250617969</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>0.0180441454753155</v>
+        <v>0.01024184757110515</v>
       </c>
       <c r="P83" s="3" t="n">
-        <v>0.02287968187633591</v>
+        <v>0.0142639934383736</v>
       </c>
     </row>
     <row r="84">
@@ -9895,7 +10261,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -9920,31 +10286,31 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_aldi_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_lightgcn_static.csv</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\aldi_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\lightgcn_static_result.json</t>
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.02214083831462619</v>
+        <v>0.01279577863692892</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.03249155514561632</v>
+        <v>0.02199442303114685</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>0.04805233237125333</v>
+        <v>0.03710101141076361</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>0.01453197936757491</v>
+        <v>0.008045619854184415</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>0.01787807671129672</v>
+        <v>0.01097523564605582</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>0.02178482402516534</v>
+        <v>0.01478044591855984</v>
       </c>
     </row>
     <row r="85">
@@ -9955,7 +10321,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>ALDI</t>
+          <t>LightGCN</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -9980,31 +10346,31 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_aldi_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_lightgcn_static.csv</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\aldi_static_result.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\lightgcn_static_result.json</t>
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.02179419370378031</v>
+        <v>0.01133603130435804</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.03193629664604191</v>
+        <v>0.01909195920331766</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.05035719404261108</v>
+        <v>0.03368911861916206</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.01426683170452728</v>
+        <v>0.007163107498823366</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0.01751944716380115</v>
+        <v>0.009633794507315111</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0.02214983319750151</v>
+        <v>0.01327973824743435</v>
       </c>
     </row>
     <row r="86">
@@ -10015,7 +10381,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -10029,7 +10395,7 @@
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>direct_all_item_macro_validated</t>
+          <t>cold_hot_course_count_weighted</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -10040,31 +10406,31 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2025_single_lr1e-5\kgrec_strict_adapter_report.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2025_single_lr1e-5\kgrec_strict_adapter_report.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_hot_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.006668783503499419</v>
+        <v>0.01718943078544417</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.01157839419786989</v>
+        <v>0.0294331506901277</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.021385325835788</v>
+        <v>0.05206270696187597</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.003839940764232707</v>
+        <v>0.01028294250920723</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.005394240973669025</v>
+        <v>0.01422220406694061</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.007851614506892615</v>
+        <v>0.01989445609878848</v>
       </c>
     </row>
     <row r="87">
@@ -10075,7 +10441,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -10089,7 +10455,7 @@
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>direct_all_item_macro_validated</t>
+          <t>cold_hot_course_count_weighted</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
@@ -10100,31 +10466,31 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2026_main_lr1e-5\kgrec_strict_adapter_report.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2026_main_lr1e-5\kgrec_strict_adapter_report.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_hot_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.005290378662431999</v>
+        <v>0.02051969384346554</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.01081479390297399</v>
+        <v>0.03431728605950973</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>0.02216727272172651</v>
+        <v>0.0569565784829144</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>0.003252437103426347</v>
+        <v>0.01266387229401928</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>0.005056875276648258</v>
+        <v>0.01712333313967939</v>
       </c>
       <c r="P87" s="3" t="n">
-        <v>0.007900423051164241</v>
+        <v>0.0227966999897219</v>
       </c>
     </row>
     <row r="88">
@@ -10135,7 +10501,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>KGRec</t>
+          <t>CCFCRec</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -10149,7 +10515,7 @@
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>direct_all_item_macro_validated</t>
+          <t>cold_hot_course_count_weighted</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
@@ -10160,31 +10526,31 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2027_main_lr1e-5\kgrec_strict_adapter_report.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2027_main_lr1e-5\kgrec_strict_adapter_report.json</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_hot_ccfcrec_static.csv</t>
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.008340103336279929</v>
+        <v>0.01918176029903175</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.01597914954329779</v>
+        <v>0.03213967686436976</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0.02826916184939728</v>
+        <v>0.05420113620327583</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0.005188999736749213</v>
+        <v>0.01230528422328989</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0.007597627355548222</v>
+        <v>0.01643268206101351</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0.01067422160871121</v>
+        <v>0.02196438386564768</v>
       </c>
     </row>
     <row r="89">
@@ -10195,7 +10561,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -10220,31 +10586,31 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_cgrc_paper_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_aldi_static.csv</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_hot_cgrc_paper_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\aldi_static_result.json</t>
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>0.03969741186069736</v>
+        <v>0.02114193879579811</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>0.06227237552774552</v>
+        <v>0.03426005367789449</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>0.09394272533696392</v>
+        <v>0.0537412506413453</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>0.02544583736418845</v>
+        <v>0.01382981632459472</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>0.03276470676178038</v>
+        <v>0.0180441454753155</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>0.04070172641728154</v>
+        <v>0.02287968187633591</v>
       </c>
     </row>
     <row r="90">
@@ -10255,7 +10621,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -10280,31 +10646,31 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_cgrc_paper_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_aldi_static.csv</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_hot_cgrc_paper_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\aldi_static_result.json</t>
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.0418389769257311</v>
+        <v>0.02214083831462619</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.06552003884217443</v>
+        <v>0.03249155514561632</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>0.09977669416710304</v>
+        <v>0.04805233237125333</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>0.02620468146187844</v>
+        <v>0.01453197936757491</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0.03378062425579789</v>
+        <v>0.01787807671129672</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>0.04240634646478214</v>
+        <v>0.02178482402516534</v>
       </c>
     </row>
     <row r="91">
@@ -10315,7 +10681,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CGRC</t>
+          <t>ALDI</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -10340,31 +10706,31 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_cgrc_paper_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_aldi_static.csv</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_hot_cgrc_paper_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\aldi_static_result.json</t>
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.04311881146219474</v>
+        <v>0.02179419370378031</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.06645874991263342</v>
+        <v>0.03193629664604191</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0.09743575307871027</v>
+        <v>0.05035719404261108</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0.02767105845266197</v>
+        <v>0.01426683170452728</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0.03516374502699694</v>
+        <v>0.01751944716380115</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0.04293971617100443</v>
+        <v>0.02214983319750151</v>
       </c>
     </row>
     <row r="92">
@@ -10375,7 +10741,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -10389,7 +10755,7 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>direct_all_item_macro_validated</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
@@ -10400,31 +10766,31 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2025_single_lr1e-5\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2025_single_lr1e-5\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.02937155583965895</v>
+        <v>0.006668783503499419</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.04472853162641222</v>
+        <v>0.01157839419786989</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.06687436850465223</v>
+        <v>0.021385325835788</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.01914323969218107</v>
+        <v>0.003839940764232707</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.02405159339698658</v>
+        <v>0.005394240973669025</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.02960819768635769</v>
+        <v>0.007851614506892615</v>
       </c>
     </row>
     <row r="93">
@@ -10435,7 +10801,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -10449,7 +10815,7 @@
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>direct_all_item_macro_validated</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
@@ -10460,31 +10826,31 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2026_main_lr1e-5\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2026_main_lr1e-5\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0.03202958210686169</v>
+        <v>0.005290378662431999</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.04664962523090035</v>
+        <v>0.01081479390297399</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>0.06849147331101647</v>
+        <v>0.02216727272172651</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>0.02101265849953772</v>
+        <v>0.003252437103426347</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>0.02572525720516753</v>
+        <v>0.005056875276648258</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>0.03117670179766287</v>
+        <v>0.007900423051164241</v>
       </c>
     </row>
     <row r="94">
@@ -10495,7 +10861,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>USIM</t>
+          <t>KGRec</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -10509,7 +10875,7 @@
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>direct_all_item_macro_validated</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
@@ -10520,31 +10886,31 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2027_main_lr1e-5\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+          <t>paper_aaai27\baseline_sources\_kgrec_strict\coco_seed2027_main_lr1e-5\kgrec_strict_adapter_report.json</t>
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>0.02926292270257883</v>
+        <v>0.008340103336279929</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.04310796387217081</v>
+        <v>0.01597914954329779</v>
       </c>
       <c r="M94" s="3" t="n">
-        <v>0.06454889082934649</v>
+        <v>0.02826916184939728</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>0.01913725753107051</v>
+        <v>0.005188999736749213</v>
       </c>
       <c r="O94" s="3" t="n">
-        <v>0.02358491047773019</v>
+        <v>0.007597627355548222</v>
       </c>
       <c r="P94" s="3" t="n">
-        <v>0.02896913201518219</v>
+        <v>0.01067422160871121</v>
       </c>
     </row>
     <row r="95">
@@ -10555,7 +10921,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -10580,31 +10946,31 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_cold_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_compare\per_item_full_hot_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>0.0270072367715849</v>
+        <v>0.03969741186069736</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.04619712373065828</v>
+        <v>0.06227237552774552</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>0.07987640631073997</v>
+        <v>0.09394272533696392</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>0.01636191562321611</v>
+        <v>0.02544583736418845</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>0.02252632661891606</v>
+        <v>0.03276470676178038</v>
       </c>
       <c r="P95" s="3" t="n">
-        <v>0.03099170512314163</v>
+        <v>0.04070172641728154</v>
       </c>
     </row>
     <row r="96">
@@ -10615,7 +10981,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -10640,31 +11006,31 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_cold_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_compare\per_item_full_hot_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.02346821646744219</v>
+        <v>0.0418389769257311</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.03879609114093215</v>
+        <v>0.06552003884217443</v>
       </c>
       <c r="M96" s="3" t="n">
-        <v>0.06317429350966029</v>
+        <v>0.09977669416710304</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>0.01520056022326479</v>
+        <v>0.02620468146187844</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>0.02012509447774968</v>
+        <v>0.03378062425579789</v>
       </c>
       <c r="P96" s="3" t="n">
-        <v>0.02620687714758125</v>
+        <v>0.04240634646478214</v>
       </c>
     </row>
     <row r="97">
@@ -10675,7 +11041,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SEMCo</t>
+          <t>CGRC</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -10700,31 +11066,31 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_cold_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_compare\per_item_full_hot_cgrc_paper_static.csv</t>
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>0.0239971712710535</v>
+        <v>0.04311881146219474</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>0.04179591863414615</v>
+        <v>0.06645874991263342</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>0.06758741767597842</v>
+        <v>0.09743575307871027</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>0.01525034448201203</v>
+        <v>0.02767105845266197</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>0.02094111541212241</v>
+        <v>0.03516374502699694</v>
       </c>
       <c r="P97" s="3" t="n">
-        <v>0.02741420107331387</v>
+        <v>0.04293971617100443</v>
       </c>
     </row>
     <row r="98">
@@ -10735,7 +11101,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -10746,45 +11112,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
         <v>820</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>6083</v>
+        <v>0</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="3" t="n">
-        <v>0.04008845476153391</v>
+        <v>0.01498026134749727</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>0.06043872664744879</v>
+        <v>0.02773264757114897</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>0.09375334585175056</v>
+        <v>0.04617360950046342</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>0.02564522727243132</v>
+        <v>0.009030346723152755</v>
       </c>
       <c r="O98" s="3" t="n">
-        <v>0.03219603075193757</v>
+        <v>0.01309921685217102</v>
       </c>
       <c r="P98" s="3" t="n">
-        <v>0.04062006760531253</v>
+        <v>0.01771123188702089</v>
       </c>
     </row>
     <row r="99">
@@ -10795,7 +11161,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -10806,45 +11172,45 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
         <v>819</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>5996</v>
+        <v>0</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
-        </is>
-      </c>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="3" t="n">
-        <v>0.04170448319991889</v>
+        <v>0.01299585316918705</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.06352171893829132</v>
+        <v>0.0255497894653098</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>0.09444379551070491</v>
+        <v>0.04835182124790376</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0.0277408845416917</v>
+        <v>0.007520444213140964</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.03471484001022643</v>
+        <v>0.01149191038396901</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.042517155337499</v>
+        <v>0.01719629204347135</v>
       </c>
     </row>
     <row r="100">
@@ -10855,7 +11221,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CKG-RL</t>
+          <t>PCGNN</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -10866,49 +11232,589 @@
           <t>ready</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>cold_hot_course_count_weighted</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
         <v>820</v>
       </c>
       <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="3" t="n">
+        <v>0.01266204596336995</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.02285109581030551</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>0.04138488693315352</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>0.007674399007025554</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0.01092593281226282</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>0.01558834909150478</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>USIM</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>6083</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.02937155583965895</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.04472853162641222</v>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>0.06687436850465223</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>0.01914323969218107</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>0.02405159339698658</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>0.02960819768635769</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>USIM</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>5996</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0.03202958210686169</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.04664962523090035</v>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>0.06849147331101647</v>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>0.02101265849953772</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>0.02572525720516753</v>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>0.03117670179766287</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>USIM</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="H103" s="2" t="n">
         <v>6065</v>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_cold_usim_official_static.csv</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\per_item_full_hot_usim_official_static.csv</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>0.02926292270257883</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>0.04310796387217081</v>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>0.06454889082934649</v>
+      </c>
+      <c r="N103" s="3" t="n">
+        <v>0.01913725753107051</v>
+      </c>
+      <c r="O103" s="3" t="n">
+        <v>0.02358491047773019</v>
+      </c>
+      <c r="P103" s="3" t="n">
+        <v>0.02896913201518219</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>6083</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2025\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>0.0270072367715849</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>0.04619712373065828</v>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>0.07987640631073997</v>
+      </c>
+      <c r="N104" s="3" t="n">
+        <v>0.01636191562321611</v>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>0.02252632661891606</v>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>0.03099170512314163</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>5996</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2026\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0.02346821646744219</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>0.03879609114093215</v>
+      </c>
+      <c r="M105" s="3" t="n">
+        <v>0.06317429350966029</v>
+      </c>
+      <c r="N105" s="3" t="n">
+        <v>0.01520056022326479</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>0.02012509447774968</v>
+      </c>
+      <c r="P105" s="3" t="n">
+        <v>0.02620687714758125</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SEMCo</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>6065</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_cold_semco_official_static.csv</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\semco_official_v1\strict_item_cold_balanced_thr1_seed_2027\sparsemax_scale12_e5_b512\per_item_full_hot_semco_official_static.csv</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>0.0239971712710535</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>0.04179591863414615</v>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>0.06758741767597842</v>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>0.01525034448201203</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>0.02094111541212241</v>
+      </c>
+      <c r="P106" s="3" t="n">
+        <v>0.02741420107331387</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>CKG-RL</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>6083</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2025\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>0.04008845476153391</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>0.06043872664744879</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>0.09375334585175056</v>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>0.02564522727243132</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>0.03219603075193757</v>
+      </c>
+      <c r="P107" s="3" t="n">
+        <v>0.04062006760531253</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>CKG-RL</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>5996</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2026\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>0.04170448319991889</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>0.06352171893829132</v>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>0.09444379551070491</v>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>0.0277408845416917</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>0.03471484001022643</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>0.042517155337499</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>CKG-RL</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>cold_hot_course_count_weighted</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>820</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>6065</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\per_item_full_cold_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>outputs\coco\single_seed_triage\ours_full\strict_item_cold_balanced_thr1_seed_2027\per_item_full_hot_usim_feedback_fast3_content_delta_static.csv</t>
         </is>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K109" s="3" t="n">
         <v>0.04303845331236298</v>
       </c>
-      <c r="L100" s="3" t="n">
+      <c r="L109" s="3" t="n">
         <v>0.06395446179683939</v>
       </c>
-      <c r="M100" s="3" t="n">
+      <c r="M109" s="3" t="n">
         <v>0.09177224614606115</v>
       </c>
-      <c r="N100" s="3" t="n">
+      <c r="N109" s="3" t="n">
         <v>0.02805727718294667</v>
       </c>
-      <c r="O100" s="3" t="n">
+      <c r="O109" s="3" t="n">
         <v>0.03475425426505819</v>
       </c>
-      <c r="P100" s="3" t="n">
+      <c r="P109" s="3" t="n">
         <v>0.04173448416415058</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P100"/>
+  <autoFilter ref="A1:P109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10925,7 +11831,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -11955,31 +12861,31 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2025\aldi_official_wsl_gpu_rerun_gate_20260717_192714\per_item_full_cold_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2025\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2025\aldi_official_wsl_gpu_rerun_gate_20260717_192714\per_item_full_hot_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.4399722553286863</v>
+        <v>0.12614181717642</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4801781512784394</v>
+        <v>0.1639968994338822</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.5214728898379688</v>
+        <v>0.2122516086304752</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.3707885957182274</v>
+        <v>0.09401705637723326</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.3837888534149859</v>
+        <v>0.1062041785433139</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3942288549707709</v>
+        <v>0.1183265612923325</v>
       </c>
     </row>
     <row r="18">
@@ -12015,31 +12921,31 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2026\aldi_official_wsl_gpu_rerun_gate_20260717_203453\per_item_full_cold_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2026\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2026\aldi_official_wsl_gpu_rerun_gate_20260717_203453\per_item_full_hot_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.455450567243436</v>
+        <v>0.1349064511201797</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5002026870742468</v>
+        <v>0.1708011778552557</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.5417958443198959</v>
+        <v>0.2210844600439146</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.3826429066345881</v>
+        <v>0.1024064376798182</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.3971737042792708</v>
+        <v>0.1139617827073767</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.407717305764997</v>
+        <v>0.1266227216400013</v>
       </c>
     </row>
     <row r="19">
@@ -12075,31 +12981,31 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2027\aldi_official_wsl_gpu_rerun_gate_20260717_205646\per_item_full_cold_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>outputs\content_delta_pop5\static_item_cold_balanced\strict_item_cold_balanced_thr1_seed_2027\main_table_balanced_itemmacro_v1\aldi_official_static_result.json</t>
+          <t>outputs\score_parity\mooccube_seed2027\aldi_official_wsl_gpu_rerun_gate_20260717_205646\per_item_full_hot_aldi_official_static.csv</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.4652876115681961</v>
+        <v>0.1538397722823481</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.5099125097780239</v>
+        <v>0.1954055883534992</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.5521278725234352</v>
+        <v>0.2431864222908143</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.3887442115832776</v>
+        <v>0.1163863386842875</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>0.4032738113722385</v>
+        <v>0.1296778832685914</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.4139647726090377</v>
+        <v>0.14171471092709</v>
       </c>
     </row>
     <row r="20">
@@ -12478,17 +13384,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -12502,17 +13408,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="3" t="n">
+        <v>0.0251347031516868</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.06225125154268782</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.1118597472130274</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0.0152533245915373</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0.02694029585339541</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.03941776121599404</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -12530,17 +13444,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
@@ -12554,17 +13468,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>0.03206210607662479</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.05436008596318311</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0.1024040058943937</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0.0196968420304419</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0.02684256037918414</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.03875188723752332</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -12582,17 +13504,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -12606,17 +13528,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\mooccube_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="3" t="n">
+        <v>0.01503636499440224</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.03931020062854771</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0.08481759132359083</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0.008423276826784943</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0.01629736444842986</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0.02760666013962692</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -14614,17 +15544,17 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
@@ -14638,17 +15568,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="3" t="n">
+        <v>0.04039911032071352</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.08790424170875298</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>0.1569145680568793</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>0.02316372239001332</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>0.03834302024784767</v>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>0.05554557407757177</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -14666,17 +15604,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
@@ -14690,17 +15628,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="3" t="n">
+        <v>0.05279864739401549</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0.1024729569572007</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0.1733169180327174</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0.0300970399065477</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>0.04598597226791548</v>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>0.06377830532821768</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -14718,17 +15664,17 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
@@ -14742,17 +15688,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\junyi_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="3" t="n">
+        <v>0.04283308620385778</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.07880763326159881</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>0.1463812515372949</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>0.024910178550486</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>0.03640083315471509</v>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>0.05330010681867861</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -16750,17 +17704,17 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
@@ -16774,17 +17728,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2025_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="3" t="n">
+        <v>0.01498026134749727</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>0.02773264757114897</v>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>0.04617360950046342</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>0.009030346723152755</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>0.01309921685217102</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>0.01771123188702089</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -16802,17 +17764,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -16826,17 +17788,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2026_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="3" t="n">
+        <v>0.01299585316918705</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>0.0255497894653098</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>0.04835182124790376</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>0.007520444213140964</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0.01149191038396901</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>0.01719629204347135</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -16854,17 +17824,17 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>unavailable_missing_warm_targets</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>retained strict report has no warm-target metrics</t>
+          <t>retained cold-target strict report; no warm-target PCGNN metrics retained</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>pcgnn_cold_target_only_report</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
@@ -16878,17 +17848,25 @@
           <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>paper_aaai27\baseline_sources\_pcgnn_strict\coco_seed2027_full_formal_kg_warm\pcgnn_strict_adapter_report.json</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-      <c r="P100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="3" t="n">
+        <v>0.01266204596336995</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>0.02285109581030551</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>0.04138488693315352</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>0.007674399007025554</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0.01092593281226282</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>0.01558834909150478</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
